--- a/LubanConfig/MiniTemplate/Datas/生成数据/#关卡设计表_1导.xlsx
+++ b/LubanConfig/MiniTemplate/Datas/生成数据/#关卡设计表_1导.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\悠手好闲\铁头工作室\方块项目设计案\《冲王》数值_cursor\LubanConfig\MiniTemplate\Datas\生成数据\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\悠手好闲\铁头工作室\方块项目设计案\《冲王》数值_cursor\新数据生成\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -55,35 +55,27 @@
   </si>
   <si>
     <t>简单</t>
-    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>森林</t>
-    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>普通</t>
-    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>草原</t>
-    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>困难</t>
-    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>雪山</t>
-    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>很难</t>
-    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>极难</t>
-    <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -99,26 +91,24 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
@@ -134,7 +124,14 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
     <border>
       <left/>
       <right/>
@@ -151,23 +148,20 @@
     </border>
   </borders>
   <cellStyleXfs count="3">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="1" applyAlignment="1">
+  <cellXfs count="3">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="2" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="2" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -537,12 +531,12 @@
         <v>10010</v>
       </c>
       <c r="C4" s="2">
-        <v>3.1</v>
-      </c>
-      <c r="D4" s="3" t="s">
+        <v>3.12</v>
+      </c>
+      <c r="D4" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="E4" s="3" t="s">
+      <c r="E4" s="2" t="s">
         <v>12</v>
       </c>
     </row>
@@ -553,10 +547,10 @@
       <c r="C5" s="2">
         <v>3.2</v>
       </c>
-      <c r="D5" s="3" t="s">
+      <c r="D5" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="E5" s="3" t="s">
+      <c r="E5" s="2" t="s">
         <v>14</v>
       </c>
     </row>
@@ -565,12 +559,12 @@
         <v>10030</v>
       </c>
       <c r="C6" s="2">
-        <v>3.4</v>
-      </c>
-      <c r="D6" s="3" t="s">
+        <v>3.36</v>
+      </c>
+      <c r="D6" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="E6" s="3" t="s">
+      <c r="E6" s="2" t="s">
         <v>16</v>
       </c>
     </row>
@@ -579,12 +573,12 @@
         <v>10040</v>
       </c>
       <c r="C7" s="2">
-        <v>3.5</v>
-      </c>
-      <c r="D7" s="3" t="s">
+        <v>3.52</v>
+      </c>
+      <c r="D7" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="E7" s="3" t="s">
+      <c r="E7" s="2" t="s">
         <v>12</v>
       </c>
     </row>
@@ -593,12 +587,12 @@
         <v>10050</v>
       </c>
       <c r="C8" s="2">
-        <v>3.7</v>
-      </c>
-      <c r="D8" s="3" t="s">
+        <v>3.6934999999999998</v>
+      </c>
+      <c r="D8" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="E8" s="3" t="s">
+      <c r="E8" s="2" t="s">
         <v>14</v>
       </c>
     </row>
@@ -607,12 +601,12 @@
         <v>10060</v>
       </c>
       <c r="C9" s="2">
-        <v>3.9</v>
-      </c>
-      <c r="D9" s="3" t="s">
+        <v>3.8689</v>
+      </c>
+      <c r="D9" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="E9" s="3" t="s">
+      <c r="E9" s="2" t="s">
         <v>16</v>
       </c>
     </row>
@@ -621,12 +615,12 @@
         <v>10070</v>
       </c>
       <c r="C10" s="2">
-        <v>4</v>
-      </c>
-      <c r="D10" s="3" t="s">
+        <v>4.0492999999999997</v>
+      </c>
+      <c r="D10" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="E10" s="3" t="s">
+      <c r="E10" s="2" t="s">
         <v>12</v>
       </c>
     </row>
@@ -635,12 +629,12 @@
         <v>10080</v>
       </c>
       <c r="C11" s="2">
-        <v>4.2</v>
-      </c>
-      <c r="D11" s="3" t="s">
+        <v>4.2213000000000003</v>
+      </c>
+      <c r="D11" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="E11" s="3" t="s">
+      <c r="E11" s="2" t="s">
         <v>14</v>
       </c>
     </row>
@@ -649,12 +643,12 @@
         <v>10090</v>
       </c>
       <c r="C12" s="2">
-        <v>4.4000000000000004</v>
-      </c>
-      <c r="D12" s="3" t="s">
+        <v>4.3935000000000004</v>
+      </c>
+      <c r="D12" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="E12" s="3" t="s">
+      <c r="E12" s="2" t="s">
         <v>16</v>
       </c>
     </row>
@@ -663,12 +657,12 @@
         <v>10100</v>
       </c>
       <c r="C13" s="2">
-        <v>4.5999999999999996</v>
-      </c>
-      <c r="D13" s="3" t="s">
+        <v>4.5682999999999998</v>
+      </c>
+      <c r="D13" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="E13" s="3" t="s">
+      <c r="E13" s="2" t="s">
         <v>12</v>
       </c>
     </row>
@@ -677,7 +671,7 @@
         <v>10110</v>
       </c>
       <c r="C14" s="2">
-        <v>4.7</v>
+        <v>4.7430000000000003</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>10</v>
@@ -691,7 +685,7 @@
         <v>10120</v>
       </c>
       <c r="C15" s="2">
-        <v>4.9000000000000004</v>
+        <v>4.9172000000000002</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>10</v>
@@ -705,7 +699,7 @@
         <v>10130</v>
       </c>
       <c r="C16" s="2">
-        <v>5.0999999999999996</v>
+        <v>5.0919999999999996</v>
       </c>
       <c r="D16" s="2" t="s">
         <v>10</v>
@@ -719,7 +713,7 @@
         <v>10140</v>
       </c>
       <c r="C17" s="2">
-        <v>5.3</v>
+        <v>5.2670000000000003</v>
       </c>
       <c r="D17" s="2" t="s">
         <v>10</v>
@@ -733,7 +727,7 @@
         <v>10150</v>
       </c>
       <c r="C18" s="2">
-        <v>5.4</v>
+        <v>5.4408000000000003</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>10</v>
@@ -747,7 +741,7 @@
         <v>10160</v>
       </c>
       <c r="C19" s="2">
-        <v>5.6</v>
+        <v>5.6146000000000003</v>
       </c>
       <c r="D19" s="2" t="s">
         <v>10</v>
@@ -761,7 +755,7 @@
         <v>10170</v>
       </c>
       <c r="C20" s="2">
-        <v>5.8</v>
+        <v>5.7888000000000002</v>
       </c>
       <c r="D20" s="2" t="s">
         <v>10</v>
@@ -775,7 +769,7 @@
         <v>10180</v>
       </c>
       <c r="C21" s="2">
-        <v>6</v>
+        <v>5.9637000000000002</v>
       </c>
       <c r="D21" s="2" t="s">
         <v>10</v>
@@ -789,7 +783,7 @@
         <v>10190</v>
       </c>
       <c r="C22" s="2">
-        <v>6.1</v>
+        <v>6.1379000000000001</v>
       </c>
       <c r="D22" s="2" t="s">
         <v>10</v>
@@ -803,7 +797,7 @@
         <v>10200</v>
       </c>
       <c r="C23" s="2">
-        <v>6.3</v>
+        <v>6.3125999999999998</v>
       </c>
       <c r="D23" s="2" t="s">
         <v>10</v>
@@ -817,7 +811,7 @@
         <v>10210</v>
       </c>
       <c r="C24" s="2">
-        <v>6.5</v>
+        <v>6.4863999999999997</v>
       </c>
       <c r="D24" s="2" t="s">
         <v>10</v>
@@ -831,7 +825,7 @@
         <v>10220</v>
       </c>
       <c r="C25" s="2">
-        <v>6.7</v>
+        <v>6.6604999999999999</v>
       </c>
       <c r="D25" s="2" t="s">
         <v>10</v>
@@ -845,7 +839,7 @@
         <v>10230</v>
       </c>
       <c r="C26" s="2">
-        <v>6.8</v>
+        <v>6.8349000000000002</v>
       </c>
       <c r="D26" s="2" t="s">
         <v>10</v>
@@ -859,7 +853,7 @@
         <v>10240</v>
       </c>
       <c r="C27" s="2">
-        <v>7</v>
+        <v>7.0083000000000002</v>
       </c>
       <c r="D27" s="2" t="s">
         <v>10</v>
@@ -873,7 +867,7 @@
         <v>10250</v>
       </c>
       <c r="C28" s="2">
-        <v>7.2</v>
+        <v>7.1832000000000003</v>
       </c>
       <c r="D28" s="2" t="s">
         <v>10</v>
@@ -887,7 +881,7 @@
         <v>10260</v>
       </c>
       <c r="C29" s="2">
-        <v>7.4</v>
+        <v>7.3582999999999998</v>
       </c>
       <c r="D29" s="2" t="s">
         <v>10</v>
@@ -901,7 +895,7 @@
         <v>10270</v>
       </c>
       <c r="C30" s="2">
-        <v>7.5</v>
+        <v>7.5328999999999997</v>
       </c>
       <c r="D30" s="2" t="s">
         <v>10</v>
@@ -915,7 +909,7 @@
         <v>10280</v>
       </c>
       <c r="C31" s="2">
-        <v>7.7</v>
+        <v>7.7065999999999999</v>
       </c>
       <c r="D31" s="2" t="s">
         <v>10</v>
@@ -929,7 +923,7 @@
         <v>10290</v>
       </c>
       <c r="C32" s="2">
-        <v>7.9</v>
+        <v>7.8804999999999996</v>
       </c>
       <c r="D32" s="2" t="s">
         <v>10</v>
@@ -943,7 +937,7 @@
         <v>10300</v>
       </c>
       <c r="C33" s="2">
-        <v>8.1</v>
+        <v>8.0551999999999992</v>
       </c>
       <c r="D33" s="2" t="s">
         <v>10</v>
@@ -957,7 +951,7 @@
         <v>10310</v>
       </c>
       <c r="C34" s="2">
-        <v>8.1999999999999993</v>
+        <v>8.2296999999999993</v>
       </c>
       <c r="D34" s="2" t="s">
         <v>10</v>
@@ -971,7 +965,7 @@
         <v>10320</v>
       </c>
       <c r="C35" s="2">
-        <v>8.4</v>
+        <v>8.4039000000000001</v>
       </c>
       <c r="D35" s="2" t="s">
         <v>10</v>
@@ -985,7 +979,7 @@
         <v>10330</v>
       </c>
       <c r="C36" s="2">
-        <v>8.6</v>
+        <v>8.5782000000000007</v>
       </c>
       <c r="D36" s="2" t="s">
         <v>10</v>
@@ -999,7 +993,7 @@
         <v>10340</v>
       </c>
       <c r="C37" s="2">
-        <v>8.8000000000000007</v>
+        <v>8.7528000000000006</v>
       </c>
       <c r="D37" s="2" t="s">
         <v>10</v>
@@ -1013,7 +1007,7 @@
         <v>10350</v>
       </c>
       <c r="C38" s="2">
-        <v>8.9</v>
+        <v>8.9265000000000008</v>
       </c>
       <c r="D38" s="2" t="s">
         <v>10</v>
@@ -1027,7 +1021,7 @@
         <v>10360</v>
       </c>
       <c r="C39" s="2">
-        <v>9.1</v>
+        <v>9.1013000000000002</v>
       </c>
       <c r="D39" s="2" t="s">
         <v>10</v>
@@ -1041,7 +1035,7 @@
         <v>10370</v>
       </c>
       <c r="C40" s="2">
-        <v>9.3000000000000007</v>
+        <v>9.2753999999999994</v>
       </c>
       <c r="D40" s="2" t="s">
         <v>10</v>
@@ -1055,7 +1049,7 @@
         <v>10380</v>
       </c>
       <c r="C41" s="2">
-        <v>9.4</v>
+        <v>9.4495000000000005</v>
       </c>
       <c r="D41" s="2" t="s">
         <v>10</v>
@@ -1069,7 +1063,7 @@
         <v>10390</v>
       </c>
       <c r="C42" s="2">
-        <v>9.6</v>
+        <v>9.6242000000000001</v>
       </c>
       <c r="D42" s="2" t="s">
         <v>10</v>
@@ -1083,7 +1077,7 @@
         <v>10400</v>
       </c>
       <c r="C43" s="2">
-        <v>9.8000000000000007</v>
+        <v>9.7982999999999993</v>
       </c>
       <c r="D43" s="2" t="s">
         <v>10</v>
@@ -1097,7 +1091,7 @@
         <v>10410</v>
       </c>
       <c r="C44" s="2">
-        <v>10</v>
+        <v>9.9724000000000004</v>
       </c>
       <c r="D44" s="2" t="s">
         <v>10</v>
@@ -1111,7 +1105,7 @@
         <v>10420</v>
       </c>
       <c r="C45" s="2">
-        <v>10.1</v>
+        <v>10.1469</v>
       </c>
       <c r="D45" s="2" t="s">
         <v>10</v>
@@ -1125,7 +1119,7 @@
         <v>10430</v>
       </c>
       <c r="C46" s="2">
-        <v>10.3</v>
+        <v>10.321099999999999</v>
       </c>
       <c r="D46" s="2" t="s">
         <v>10</v>
@@ -1139,7 +1133,7 @@
         <v>10440</v>
       </c>
       <c r="C47" s="2">
-        <v>10.5</v>
+        <v>10.495900000000001</v>
       </c>
       <c r="D47" s="2" t="s">
         <v>10</v>
@@ -1153,7 +1147,7 @@
         <v>10450</v>
       </c>
       <c r="C48" s="2">
-        <v>10.7</v>
+        <v>10.669499999999999</v>
       </c>
       <c r="D48" s="2" t="s">
         <v>10</v>
@@ -1167,7 +1161,7 @@
         <v>10460</v>
       </c>
       <c r="C49" s="2">
-        <v>10.8</v>
+        <v>10.844200000000001</v>
       </c>
       <c r="D49" s="2" t="s">
         <v>10</v>
@@ -1181,7 +1175,7 @@
         <v>10470</v>
       </c>
       <c r="C50" s="2">
-        <v>11</v>
+        <v>11.0185</v>
       </c>
       <c r="D50" s="2" t="s">
         <v>10</v>
@@ -1195,7 +1189,7 @@
         <v>10480</v>
       </c>
       <c r="C51" s="2">
-        <v>11.2</v>
+        <v>11.1927</v>
       </c>
       <c r="D51" s="2" t="s">
         <v>10</v>
@@ -1209,7 +1203,7 @@
         <v>10490</v>
       </c>
       <c r="C52" s="2">
-        <v>11.4</v>
+        <v>11.367599999999999</v>
       </c>
       <c r="D52" s="2" t="s">
         <v>10</v>
@@ -1223,7 +1217,7 @@
         <v>10500</v>
       </c>
       <c r="C53" s="2">
-        <v>11.5</v>
+        <v>11.541600000000001</v>
       </c>
       <c r="D53" s="2" t="s">
         <v>10</v>
@@ -1237,7 +1231,7 @@
         <v>10510</v>
       </c>
       <c r="C54" s="2">
-        <v>11.7</v>
+        <v>11.7158</v>
       </c>
       <c r="D54" s="2" t="s">
         <v>10</v>
@@ -1251,7 +1245,7 @@
         <v>10520</v>
       </c>
       <c r="C55" s="2">
-        <v>11.9</v>
+        <v>11.889799999999999</v>
       </c>
       <c r="D55" s="2" t="s">
         <v>10</v>
@@ -1265,7 +1259,7 @@
         <v>10530</v>
       </c>
       <c r="C56" s="2">
-        <v>12.1</v>
+        <v>12.064500000000001</v>
       </c>
       <c r="D56" s="2" t="s">
         <v>10</v>
@@ -1279,7 +1273,7 @@
         <v>10540</v>
       </c>
       <c r="C57" s="2">
-        <v>12.2</v>
+        <v>12.238799999999999</v>
       </c>
       <c r="D57" s="2" t="s">
         <v>10</v>
@@ -1293,7 +1287,7 @@
         <v>10550</v>
       </c>
       <c r="C58" s="2">
-        <v>12.4</v>
+        <v>12.4129</v>
       </c>
       <c r="D58" s="2" t="s">
         <v>10</v>
@@ -1307,7 +1301,7 @@
         <v>10560</v>
       </c>
       <c r="C59" s="2">
-        <v>12.6</v>
+        <v>12.5871</v>
       </c>
       <c r="D59" s="2" t="s">
         <v>10</v>
@@ -1321,7 +1315,7 @@
         <v>10570</v>
       </c>
       <c r="C60" s="2">
-        <v>12.8</v>
+        <v>12.760999999999999</v>
       </c>
       <c r="D60" s="2" t="s">
         <v>10</v>
@@ -1335,7 +1329,7 @@
         <v>10580</v>
       </c>
       <c r="C61" s="2">
-        <v>12.9</v>
+        <v>12.935700000000001</v>
       </c>
       <c r="D61" s="2" t="s">
         <v>10</v>
@@ -1349,7 +1343,7 @@
         <v>10590</v>
       </c>
       <c r="C62" s="2">
-        <v>13.1</v>
+        <v>13.110200000000001</v>
       </c>
       <c r="D62" s="2" t="s">
         <v>10</v>
@@ -1363,7 +1357,7 @@
         <v>10600</v>
       </c>
       <c r="C63" s="2">
-        <v>13.3</v>
+        <v>13.2845</v>
       </c>
       <c r="D63" s="2" t="s">
         <v>10</v>
@@ -1377,7 +1371,7 @@
         <v>10610</v>
       </c>
       <c r="C64" s="2">
-        <v>13.5</v>
+        <v>13.458399999999999</v>
       </c>
       <c r="D64" s="2" t="s">
         <v>10</v>
@@ -1391,7 +1385,7 @@
         <v>10620</v>
       </c>
       <c r="C65" s="2">
-        <v>13.6</v>
+        <v>13.6328</v>
       </c>
       <c r="D65" s="2" t="s">
         <v>10</v>
@@ -1405,7 +1399,7 @@
         <v>10630</v>
       </c>
       <c r="C66" s="2">
-        <v>13.8</v>
+        <v>13.807499999999999</v>
       </c>
       <c r="D66" s="2" t="s">
         <v>10</v>
@@ -1419,7 +1413,7 @@
         <v>10640</v>
       </c>
       <c r="C67" s="2">
-        <v>14</v>
+        <v>13.981999999999999</v>
       </c>
       <c r="D67" s="2" t="s">
         <v>10</v>
@@ -1433,7 +1427,7 @@
         <v>10650</v>
       </c>
       <c r="C68" s="2">
-        <v>14.2</v>
+        <v>14.156700000000001</v>
       </c>
       <c r="D68" s="2" t="s">
         <v>10</v>
@@ -1447,7 +1441,7 @@
         <v>10660</v>
       </c>
       <c r="C69" s="2">
-        <v>14.3</v>
+        <v>14.3307</v>
       </c>
       <c r="D69" s="2" t="s">
         <v>10</v>
@@ -1461,7 +1455,7 @@
         <v>10670</v>
       </c>
       <c r="C70" s="2">
-        <v>14.5</v>
+        <v>14.505100000000001</v>
       </c>
       <c r="D70" s="2" t="s">
         <v>10</v>
@@ -1475,7 +1469,7 @@
         <v>10680</v>
       </c>
       <c r="C71" s="2">
-        <v>14.7</v>
+        <v>14.6793</v>
       </c>
       <c r="D71" s="2" t="s">
         <v>10</v>
@@ -1489,7 +1483,7 @@
         <v>10690</v>
       </c>
       <c r="C72" s="2">
-        <v>14.9</v>
+        <v>14.853300000000001</v>
       </c>
       <c r="D72" s="2" t="s">
         <v>10</v>
@@ -1503,7 +1497,7 @@
         <v>10700</v>
       </c>
       <c r="C73" s="2">
-        <v>15</v>
+        <v>15.027900000000001</v>
       </c>
       <c r="D73" s="2" t="s">
         <v>10</v>
@@ -1517,7 +1511,7 @@
         <v>10710</v>
       </c>
       <c r="C74" s="2">
-        <v>15.2</v>
+        <v>15.202400000000001</v>
       </c>
       <c r="D74" s="2" t="s">
         <v>10</v>
@@ -1531,7 +1525,7 @@
         <v>10720</v>
       </c>
       <c r="C75" s="2">
-        <v>15.4</v>
+        <v>15.3766</v>
       </c>
       <c r="D75" s="2" t="s">
         <v>10</v>
@@ -1545,7 +1539,7 @@
         <v>10730</v>
       </c>
       <c r="C76" s="2">
-        <v>15.6</v>
+        <v>15.5504</v>
       </c>
       <c r="D76" s="2" t="s">
         <v>10</v>
@@ -1559,7 +1553,7 @@
         <v>10740</v>
       </c>
       <c r="C77" s="2">
-        <v>15.7</v>
+        <v>15.725</v>
       </c>
       <c r="D77" s="2" t="s">
         <v>10</v>
@@ -1573,7 +1567,7 @@
         <v>10750</v>
       </c>
       <c r="C78" s="2">
-        <v>15.9</v>
+        <v>15.8992</v>
       </c>
       <c r="D78" s="2" t="s">
         <v>10</v>
@@ -1587,7 +1581,7 @@
         <v>10760</v>
       </c>
       <c r="C79" s="2">
-        <v>16.100000000000001</v>
+        <v>16.0731</v>
       </c>
       <c r="D79" s="2" t="s">
         <v>10</v>
@@ -1601,7 +1595,7 @@
         <v>10770</v>
       </c>
       <c r="C80" s="2">
-        <v>16.2</v>
+        <v>16.247599999999998</v>
       </c>
       <c r="D80" s="2" t="s">
         <v>10</v>
@@ -1615,7 +1609,7 @@
         <v>10780</v>
       </c>
       <c r="C81" s="2">
-        <v>16.399999999999999</v>
+        <v>16.4224</v>
       </c>
       <c r="D81" s="2" t="s">
         <v>10</v>
@@ -1629,7 +1623,7 @@
         <v>10790</v>
       </c>
       <c r="C82" s="2">
-        <v>16.600000000000001</v>
+        <v>16.597000000000001</v>
       </c>
       <c r="D82" s="2" t="s">
         <v>10</v>
@@ -1643,7 +1637,7 @@
         <v>10800</v>
       </c>
       <c r="C83" s="2">
-        <v>16.8</v>
+        <v>16.7715</v>
       </c>
       <c r="D83" s="2" t="s">
         <v>10</v>
@@ -1657,7 +1651,7 @@
         <v>10810</v>
       </c>
       <c r="C84" s="2">
-        <v>16.899999999999999</v>
+        <v>16.945799999999998</v>
       </c>
       <c r="D84" s="2" t="s">
         <v>10</v>
@@ -1671,7 +1665,7 @@
         <v>10820</v>
       </c>
       <c r="C85" s="2">
-        <v>17.100000000000001</v>
+        <v>17.119700000000002</v>
       </c>
       <c r="D85" s="2" t="s">
         <v>10</v>
@@ -1685,7 +1679,7 @@
         <v>10830</v>
       </c>
       <c r="C86" s="2">
-        <v>17.3</v>
+        <v>17.294</v>
       </c>
       <c r="D86" s="2" t="s">
         <v>10</v>
@@ -1699,7 +1693,7 @@
         <v>10840</v>
       </c>
       <c r="C87" s="2">
-        <v>17.5</v>
+        <v>17.468499999999999</v>
       </c>
       <c r="D87" s="2" t="s">
         <v>10</v>
@@ -1713,7 +1707,7 @@
         <v>10850</v>
       </c>
       <c r="C88" s="2">
-        <v>17.600000000000001</v>
+        <v>17.6434</v>
       </c>
       <c r="D88" s="2" t="s">
         <v>10</v>
@@ -1727,7 +1721,7 @@
         <v>10860</v>
       </c>
       <c r="C89" s="2">
-        <v>17.8</v>
+        <v>17.8172</v>
       </c>
       <c r="D89" s="2" t="s">
         <v>10</v>
@@ -1741,7 +1735,7 @@
         <v>10870</v>
       </c>
       <c r="C90" s="2">
-        <v>18</v>
+        <v>17.991499999999998</v>
       </c>
       <c r="D90" s="2" t="s">
         <v>10</v>
@@ -1755,7 +1749,7 @@
         <v>10880</v>
       </c>
       <c r="C91" s="2">
-        <v>18.2</v>
+        <v>18.165199999999999</v>
       </c>
       <c r="D91" s="2" t="s">
         <v>10</v>
@@ -1769,7 +1763,7 @@
         <v>10890</v>
       </c>
       <c r="C92" s="2">
-        <v>18.3</v>
+        <v>18.339400000000001</v>
       </c>
       <c r="D92" s="2" t="s">
         <v>10</v>
@@ -1783,7 +1777,7 @@
         <v>10900</v>
       </c>
       <c r="C93" s="2">
-        <v>18.5</v>
+        <v>18.513400000000001</v>
       </c>
       <c r="D93" s="2" t="s">
         <v>10</v>
@@ -1797,7 +1791,7 @@
         <v>10910</v>
       </c>
       <c r="C94" s="2">
-        <v>18.7</v>
+        <v>18.688700000000001</v>
       </c>
       <c r="D94" s="2" t="s">
         <v>10</v>
@@ -1811,7 +1805,7 @@
         <v>10920</v>
       </c>
       <c r="C95" s="2">
-        <v>18.899999999999999</v>
+        <v>18.863099999999999</v>
       </c>
       <c r="D95" s="2" t="s">
         <v>10</v>
@@ -1825,7 +1819,7 @@
         <v>10930</v>
       </c>
       <c r="C96" s="2">
-        <v>19</v>
+        <v>19.036899999999999</v>
       </c>
       <c r="D96" s="2" t="s">
         <v>10</v>
@@ -1839,7 +1833,7 @@
         <v>10940</v>
       </c>
       <c r="C97" s="2">
-        <v>19.2</v>
+        <v>19.210699999999999</v>
       </c>
       <c r="D97" s="2" t="s">
         <v>10</v>
@@ -1853,7 +1847,7 @@
         <v>10950</v>
       </c>
       <c r="C98" s="2">
-        <v>19.399999999999999</v>
+        <v>19.385200000000001</v>
       </c>
       <c r="D98" s="2" t="s">
         <v>10</v>
@@ -1867,7 +1861,7 @@
         <v>10960</v>
       </c>
       <c r="C99" s="2">
-        <v>19.600000000000001</v>
+        <v>19.559899999999999</v>
       </c>
       <c r="D99" s="2" t="s">
         <v>10</v>
@@ -1881,7 +1875,7 @@
         <v>10970</v>
       </c>
       <c r="C100" s="2">
-        <v>19.7</v>
+        <v>19.733699999999999</v>
       </c>
       <c r="D100" s="2" t="s">
         <v>10</v>
@@ -1895,7 +1889,7 @@
         <v>10980</v>
       </c>
       <c r="C101" s="2">
-        <v>19.899999999999999</v>
+        <v>19.907800000000002</v>
       </c>
       <c r="D101" s="2" t="s">
         <v>10</v>
@@ -1909,7 +1903,7 @@
         <v>10990</v>
       </c>
       <c r="C102" s="2">
-        <v>20.100000000000001</v>
+        <v>20.0822</v>
       </c>
       <c r="D102" s="2" t="s">
         <v>10</v>
@@ -1923,7 +1917,7 @@
         <v>11000</v>
       </c>
       <c r="C103" s="2">
-        <v>20.2</v>
+        <v>20.198699999999999</v>
       </c>
       <c r="D103" s="2" t="s">
         <v>10</v>
@@ -1933,7 +1927,8 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="3" type="noConversion"/>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/LubanConfig/MiniTemplate/Datas/生成数据/#关卡设计表_1导.xlsx
+++ b/LubanConfig/MiniTemplate/Datas/生成数据/#关卡设计表_1导.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\悠手好闲\铁头工作室\方块项目设计案\《冲王》数值_cursor\新数据生成\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\悠手好闲\铁头工作室\方块项目设计案\《冲王》数值_cursor\LubanConfig\MiniTemplate\Datas\生成数据\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="26">
   <si>
     <t>##var</t>
   </si>
@@ -66,9 +66,6 @@
     <t>简单</t>
   </si>
   <si>
-    <t>森林</t>
-  </si>
-  <si>
     <t>普通</t>
   </si>
   <si>
@@ -80,12 +77,52 @@
   <si>
     <t>极难</t>
   </si>
+  <si>
+    <t>Forest</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Autumn</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Desert</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>D</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>arkland</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Lava</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Skyland</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Winter</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -105,12 +142,21 @@
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
   </fonts>
@@ -159,12 +205,15 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="2" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="2" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -561,7 +610,7 @@
         <v>10010</v>
       </c>
       <c r="C4" s="2">
-        <v>3.12</v>
+        <v>3.2</v>
       </c>
       <c r="D4" s="2">
         <v>2</v>
@@ -575,8 +624,8 @@
       <c r="G4" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="H4" s="2" t="s">
-        <v>15</v>
+      <c r="H4" s="3" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.15">
@@ -584,22 +633,22 @@
         <v>10020</v>
       </c>
       <c r="C5" s="2">
-        <v>3.2</v>
+        <v>3.64</v>
       </c>
       <c r="D5" s="2">
+        <v>3</v>
+      </c>
+      <c r="E5" s="2">
         <v>2</v>
-      </c>
-      <c r="E5" s="2">
-        <v>1</v>
       </c>
       <c r="F5" s="2">
         <v>1</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>15</v>
+        <v>15</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.15">
@@ -607,22 +656,22 @@
         <v>10030</v>
       </c>
       <c r="C6" s="2">
-        <v>3.36</v>
+        <v>4.2736000000000001</v>
       </c>
       <c r="D6" s="2">
+        <v>3</v>
+      </c>
+      <c r="E6" s="2">
         <v>2</v>
       </c>
-      <c r="E6" s="2">
-        <v>1</v>
-      </c>
       <c r="F6" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.15">
@@ -630,22 +679,22 @@
         <v>10040</v>
       </c>
       <c r="C7" s="2">
-        <v>3.52</v>
+        <v>4.9029999999999996</v>
       </c>
       <c r="D7" s="2">
+        <v>4</v>
+      </c>
+      <c r="E7" s="2">
         <v>3</v>
       </c>
-      <c r="E7" s="2">
-        <v>1</v>
-      </c>
       <c r="F7" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="H7" s="2" t="s">
-        <v>15</v>
+        <v>17</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.15">
@@ -653,22 +702,22 @@
         <v>10050</v>
       </c>
       <c r="C8" s="2">
-        <v>3.6934999999999998</v>
+        <v>5.5392000000000001</v>
       </c>
       <c r="D8" s="2">
+        <v>5</v>
+      </c>
+      <c r="E8" s="2">
+        <v>4</v>
+      </c>
+      <c r="F8" s="2">
         <v>3</v>
       </c>
-      <c r="E8" s="2">
-        <v>2</v>
-      </c>
-      <c r="F8" s="2">
-        <v>1</v>
-      </c>
       <c r="G8" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="H8" s="2" t="s">
-        <v>15</v>
+        <v>18</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.15">
@@ -676,22 +725,22 @@
         <v>10060</v>
       </c>
       <c r="C9" s="2">
-        <v>3.8689</v>
+        <v>6.1727999999999996</v>
       </c>
       <c r="D9" s="2">
+        <v>5</v>
+      </c>
+      <c r="E9" s="2">
         <v>4</v>
       </c>
-      <c r="E9" s="2">
-        <v>2</v>
-      </c>
       <c r="F9" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="H9" s="2" t="s">
-        <v>15</v>
+      <c r="H9" s="3" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.15">
@@ -699,22 +748,22 @@
         <v>10070</v>
       </c>
       <c r="C10" s="2">
-        <v>4.0492999999999997</v>
+        <v>6.8060999999999998</v>
       </c>
       <c r="D10" s="2">
+        <v>6</v>
+      </c>
+      <c r="E10" s="2">
+        <v>5</v>
+      </c>
+      <c r="F10" s="2">
         <v>4</v>
       </c>
-      <c r="E10" s="2">
-        <v>3</v>
-      </c>
-      <c r="F10" s="2">
-        <v>1</v>
-      </c>
       <c r="G10" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="H10" s="2" t="s">
-        <v>15</v>
+        <v>15</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.15">
@@ -722,108 +771,92 @@
         <v>10080</v>
       </c>
       <c r="C11" s="2">
-        <v>4.2213000000000003</v>
+        <v>7.4424000000000001</v>
       </c>
       <c r="D11" s="2">
+        <v>6</v>
+      </c>
+      <c r="E11" s="2">
         <v>5</v>
       </c>
-      <c r="E11" s="2">
-        <v>3</v>
-      </c>
       <c r="F11" s="2">
-        <v>2</v>
-      </c>
-      <c r="G11" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="H11" s="2" t="s">
-        <v>15</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="G11" s="2"/>
+      <c r="H11" s="2"/>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.15">
       <c r="B12" s="2">
         <v>10090</v>
       </c>
       <c r="C12" s="2">
-        <v>4.3935000000000004</v>
+        <v>8.0686999999999998</v>
       </c>
       <c r="D12" s="2">
+        <v>7</v>
+      </c>
+      <c r="E12" s="2">
+        <v>6</v>
+      </c>
+      <c r="F12" s="2">
         <v>5</v>
       </c>
-      <c r="E12" s="2">
-        <v>3</v>
-      </c>
-      <c r="F12" s="2">
-        <v>2</v>
-      </c>
-      <c r="G12" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="H12" s="2" t="s">
-        <v>15</v>
-      </c>
+      <c r="G12" s="2"/>
+      <c r="H12" s="2"/>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.15">
       <c r="B13" s="2">
         <v>10100</v>
       </c>
       <c r="C13" s="2">
-        <v>4.5682999999999998</v>
+        <v>8.7048000000000005</v>
       </c>
       <c r="D13" s="2">
+        <v>7</v>
+      </c>
+      <c r="E13" s="2">
+        <v>6</v>
+      </c>
+      <c r="F13" s="2">
         <v>5</v>
       </c>
-      <c r="E13" s="2">
-        <v>4</v>
-      </c>
-      <c r="F13" s="2">
-        <v>2</v>
-      </c>
-      <c r="G13" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="H13" s="2" t="s">
-        <v>15</v>
-      </c>
+      <c r="G13" s="2"/>
+      <c r="H13" s="2"/>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.15">
       <c r="B14" s="2">
         <v>10110</v>
       </c>
       <c r="C14" s="2">
-        <v>4.7430000000000003</v>
+        <v>9.3439999999999994</v>
       </c>
       <c r="D14" s="2">
+        <v>8</v>
+      </c>
+      <c r="E14" s="2">
+        <v>7</v>
+      </c>
+      <c r="F14" s="2">
         <v>6</v>
       </c>
-      <c r="E14" s="2">
-        <v>4</v>
-      </c>
-      <c r="F14" s="2">
-        <v>3</v>
-      </c>
-      <c r="G14" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="H14" s="2" t="s">
-        <v>15</v>
-      </c>
+      <c r="G14" s="2"/>
+      <c r="H14" s="2"/>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.15">
       <c r="B15" s="2">
         <v>10120</v>
       </c>
       <c r="C15" s="2">
-        <v>4.9172000000000002</v>
+        <v>9.9699000000000009</v>
       </c>
       <c r="D15" s="2">
+        <v>8</v>
+      </c>
+      <c r="E15" s="2">
+        <v>7</v>
+      </c>
+      <c r="F15" s="2">
         <v>6</v>
-      </c>
-      <c r="E15" s="2">
-        <v>4</v>
-      </c>
-      <c r="F15" s="2">
-        <v>3</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>13</v>
@@ -837,16 +870,16 @@
         <v>10130</v>
       </c>
       <c r="C16" s="2">
-        <v>5.0919999999999996</v>
+        <v>10.6028</v>
       </c>
       <c r="D16" s="2">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E16" s="2">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F16" s="2">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="G16" s="2" t="s">
         <v>13</v>
@@ -860,16 +893,16 @@
         <v>10140</v>
       </c>
       <c r="C17" s="2">
-        <v>5.2670000000000003</v>
+        <v>11.232900000000001</v>
       </c>
       <c r="D17" s="2">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E17" s="2">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F17" s="2">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="G17" s="2" t="s">
         <v>13</v>
@@ -883,16 +916,16 @@
         <v>10150</v>
       </c>
       <c r="C18" s="2">
-        <v>5.4408000000000003</v>
+        <v>11.8788</v>
       </c>
       <c r="D18" s="2">
+        <v>9</v>
+      </c>
+      <c r="E18" s="2">
+        <v>8</v>
+      </c>
+      <c r="F18" s="2">
         <v>7</v>
-      </c>
-      <c r="E18" s="2">
-        <v>5</v>
-      </c>
-      <c r="F18" s="2">
-        <v>4</v>
       </c>
       <c r="G18" s="2" t="s">
         <v>13</v>
@@ -906,16 +939,16 @@
         <v>10160</v>
       </c>
       <c r="C19" s="2">
-        <v>5.6146000000000003</v>
+        <v>12.5076</v>
       </c>
       <c r="D19" s="2">
+        <v>9</v>
+      </c>
+      <c r="E19" s="2">
+        <v>8</v>
+      </c>
+      <c r="F19" s="2">
         <v>7</v>
-      </c>
-      <c r="E19" s="2">
-        <v>5</v>
-      </c>
-      <c r="F19" s="2">
-        <v>4</v>
       </c>
       <c r="G19" s="2" t="s">
         <v>13</v>
@@ -929,16 +962,16 @@
         <v>10170</v>
       </c>
       <c r="C20" s="2">
-        <v>5.7888000000000002</v>
+        <v>13.1393</v>
       </c>
       <c r="D20" s="2">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E20" s="2">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F20" s="2">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="G20" s="2" t="s">
         <v>13</v>
@@ -952,16 +985,16 @@
         <v>10180</v>
       </c>
       <c r="C21" s="2">
-        <v>5.9637000000000002</v>
+        <v>13.7729</v>
       </c>
       <c r="D21" s="2">
+        <v>10</v>
+      </c>
+      <c r="E21" s="2">
+        <v>9</v>
+      </c>
+      <c r="F21" s="2">
         <v>8</v>
-      </c>
-      <c r="E21" s="2">
-        <v>6</v>
-      </c>
-      <c r="F21" s="2">
-        <v>5</v>
       </c>
       <c r="G21" s="2" t="s">
         <v>13</v>
@@ -975,16 +1008,16 @@
         <v>10190</v>
       </c>
       <c r="C22" s="2">
-        <v>6.1379000000000001</v>
+        <v>14.408200000000001</v>
       </c>
       <c r="D22" s="2">
+        <v>10</v>
+      </c>
+      <c r="E22" s="2">
+        <v>9</v>
+      </c>
+      <c r="F22" s="2">
         <v>8</v>
-      </c>
-      <c r="E22" s="2">
-        <v>6</v>
-      </c>
-      <c r="F22" s="2">
-        <v>5</v>
       </c>
       <c r="G22" s="2" t="s">
         <v>13</v>
@@ -998,16 +1031,16 @@
         <v>10200</v>
       </c>
       <c r="C23" s="2">
-        <v>6.3125999999999998</v>
+        <v>15.042400000000001</v>
       </c>
       <c r="D23" s="2">
+        <v>10</v>
+      </c>
+      <c r="E23" s="2">
+        <v>9</v>
+      </c>
+      <c r="F23" s="2">
         <v>8</v>
-      </c>
-      <c r="E23" s="2">
-        <v>6</v>
-      </c>
-      <c r="F23" s="2">
-        <v>5</v>
       </c>
       <c r="G23" s="2" t="s">
         <v>13</v>
@@ -1021,16 +1054,16 @@
         <v>10210</v>
       </c>
       <c r="C24" s="2">
-        <v>6.4863999999999997</v>
+        <v>15.676</v>
       </c>
       <c r="D24" s="2">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E24" s="2">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F24" s="2">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="G24" s="2" t="s">
         <v>13</v>
@@ -1044,16 +1077,16 @@
         <v>10220</v>
       </c>
       <c r="C25" s="2">
-        <v>6.6604999999999999</v>
+        <v>16.310500000000001</v>
       </c>
       <c r="D25" s="2">
+        <v>11</v>
+      </c>
+      <c r="E25" s="2">
+        <v>10</v>
+      </c>
+      <c r="F25" s="2">
         <v>9</v>
-      </c>
-      <c r="E25" s="2">
-        <v>7</v>
-      </c>
-      <c r="F25" s="2">
-        <v>6</v>
       </c>
       <c r="G25" s="2" t="s">
         <v>13</v>
@@ -1067,16 +1100,16 @@
         <v>10230</v>
       </c>
       <c r="C26" s="2">
-        <v>6.8349000000000002</v>
+        <v>16.9422</v>
       </c>
       <c r="D26" s="2">
+        <v>11</v>
+      </c>
+      <c r="E26" s="2">
+        <v>10</v>
+      </c>
+      <c r="F26" s="2">
         <v>9</v>
-      </c>
-      <c r="E26" s="2">
-        <v>7</v>
-      </c>
-      <c r="F26" s="2">
-        <v>6</v>
       </c>
       <c r="G26" s="2" t="s">
         <v>13</v>
@@ -1090,16 +1123,16 @@
         <v>10240</v>
       </c>
       <c r="C27" s="2">
-        <v>7.0083000000000002</v>
+        <v>17.5779</v>
       </c>
       <c r="D27" s="2">
+        <v>11</v>
+      </c>
+      <c r="E27" s="2">
+        <v>10</v>
+      </c>
+      <c r="F27" s="2">
         <v>9</v>
-      </c>
-      <c r="E27" s="2">
-        <v>7</v>
-      </c>
-      <c r="F27" s="2">
-        <v>6</v>
       </c>
       <c r="G27" s="2" t="s">
         <v>13</v>
@@ -1113,16 +1146,16 @@
         <v>10250</v>
       </c>
       <c r="C28" s="2">
-        <v>7.1832000000000003</v>
+        <v>18.2134</v>
       </c>
       <c r="D28" s="2">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E28" s="2">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F28" s="2">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G28" s="2" t="s">
         <v>13</v>
@@ -1136,16 +1169,16 @@
         <v>10260</v>
       </c>
       <c r="C29" s="2">
-        <v>7.3582999999999998</v>
+        <v>18.845099999999999</v>
       </c>
       <c r="D29" s="2">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E29" s="2">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F29" s="2">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G29" s="2" t="s">
         <v>13</v>
@@ -1159,16 +1192,16 @@
         <v>10270</v>
       </c>
       <c r="C30" s="2">
-        <v>7.5328999999999997</v>
+        <v>19.4834</v>
       </c>
       <c r="D30" s="2">
+        <v>12</v>
+      </c>
+      <c r="E30" s="2">
+        <v>11</v>
+      </c>
+      <c r="F30" s="2">
         <v>10</v>
-      </c>
-      <c r="E30" s="2">
-        <v>8</v>
-      </c>
-      <c r="F30" s="2">
-        <v>7</v>
       </c>
       <c r="G30" s="2" t="s">
         <v>13</v>
@@ -1182,16 +1215,16 @@
         <v>10280</v>
       </c>
       <c r="C31" s="2">
-        <v>7.7065999999999999</v>
+        <v>20.1143</v>
       </c>
       <c r="D31" s="2">
+        <v>12</v>
+      </c>
+      <c r="E31" s="2">
+        <v>11</v>
+      </c>
+      <c r="F31" s="2">
         <v>10</v>
-      </c>
-      <c r="E31" s="2">
-        <v>8</v>
-      </c>
-      <c r="F31" s="2">
-        <v>7</v>
       </c>
       <c r="G31" s="2" t="s">
         <v>13</v>
@@ -1205,16 +1238,16 @@
         <v>10290</v>
       </c>
       <c r="C32" s="2">
-        <v>7.8804999999999996</v>
+        <v>20.747900000000001</v>
       </c>
       <c r="D32" s="2">
+        <v>12</v>
+      </c>
+      <c r="E32" s="2">
+        <v>11</v>
+      </c>
+      <c r="F32" s="2">
         <v>10</v>
-      </c>
-      <c r="E32" s="2">
-        <v>8</v>
-      </c>
-      <c r="F32" s="2">
-        <v>7</v>
       </c>
       <c r="G32" s="2" t="s">
         <v>13</v>
@@ -1228,16 +1261,16 @@
         <v>10300</v>
       </c>
       <c r="C33" s="2">
-        <v>8.0551999999999992</v>
+        <v>21.382899999999999</v>
       </c>
       <c r="D33" s="2">
+        <v>12</v>
+      </c>
+      <c r="E33" s="2">
+        <v>11</v>
+      </c>
+      <c r="F33" s="2">
         <v>10</v>
-      </c>
-      <c r="E33" s="2">
-        <v>9</v>
-      </c>
-      <c r="F33" s="2">
-        <v>7</v>
       </c>
       <c r="G33" s="2" t="s">
         <v>13</v>
@@ -1251,16 +1284,16 @@
         <v>10310</v>
       </c>
       <c r="C34" s="2">
-        <v>8.2296999999999993</v>
+        <v>22.0169</v>
       </c>
       <c r="D34" s="2">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E34" s="2">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F34" s="2">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="G34" s="2" t="s">
         <v>13</v>
@@ -1274,16 +1307,16 @@
         <v>10320</v>
       </c>
       <c r="C35" s="2">
-        <v>8.4039000000000001</v>
+        <v>22.653700000000001</v>
       </c>
       <c r="D35" s="2">
+        <v>13</v>
+      </c>
+      <c r="E35" s="2">
+        <v>12</v>
+      </c>
+      <c r="F35" s="2">
         <v>11</v>
-      </c>
-      <c r="E35" s="2">
-        <v>9</v>
-      </c>
-      <c r="F35" s="2">
-        <v>8</v>
       </c>
       <c r="G35" s="2" t="s">
         <v>13</v>
@@ -1297,16 +1330,16 @@
         <v>10330</v>
       </c>
       <c r="C36" s="2">
-        <v>8.5782000000000007</v>
+        <v>23.286000000000001</v>
       </c>
       <c r="D36" s="2">
+        <v>13</v>
+      </c>
+      <c r="E36" s="2">
+        <v>12</v>
+      </c>
+      <c r="F36" s="2">
         <v>11</v>
-      </c>
-      <c r="E36" s="2">
-        <v>9</v>
-      </c>
-      <c r="F36" s="2">
-        <v>8</v>
       </c>
       <c r="G36" s="2" t="s">
         <v>13</v>
@@ -1320,16 +1353,16 @@
         <v>10340</v>
       </c>
       <c r="C37" s="2">
-        <v>8.7528000000000006</v>
+        <v>23.915099999999999</v>
       </c>
       <c r="D37" s="2">
+        <v>13</v>
+      </c>
+      <c r="E37" s="2">
+        <v>12</v>
+      </c>
+      <c r="F37" s="2">
         <v>11</v>
-      </c>
-      <c r="E37" s="2">
-        <v>9</v>
-      </c>
-      <c r="F37" s="2">
-        <v>8</v>
       </c>
       <c r="G37" s="2" t="s">
         <v>13</v>
@@ -1343,16 +1376,16 @@
         <v>10350</v>
       </c>
       <c r="C38" s="2">
-        <v>8.9265000000000008</v>
+        <v>24.544</v>
       </c>
       <c r="D38" s="2">
+        <v>13</v>
+      </c>
+      <c r="E38" s="2">
+        <v>12</v>
+      </c>
+      <c r="F38" s="2">
         <v>11</v>
-      </c>
-      <c r="E38" s="2">
-        <v>10</v>
-      </c>
-      <c r="F38" s="2">
-        <v>8</v>
       </c>
       <c r="G38" s="2" t="s">
         <v>13</v>
@@ -1366,16 +1399,16 @@
         <v>10360</v>
       </c>
       <c r="C39" s="2">
-        <v>9.1013000000000002</v>
+        <v>25.181899999999999</v>
       </c>
       <c r="D39" s="2">
+        <v>13</v>
+      </c>
+      <c r="E39" s="2">
+        <v>12</v>
+      </c>
+      <c r="F39" s="2">
         <v>11</v>
-      </c>
-      <c r="E39" s="2">
-        <v>10</v>
-      </c>
-      <c r="F39" s="2">
-        <v>8</v>
       </c>
       <c r="G39" s="2" t="s">
         <v>13</v>
@@ -1389,16 +1422,16 @@
         <v>10370</v>
       </c>
       <c r="C40" s="2">
-        <v>9.2753999999999994</v>
+        <v>25.820699999999999</v>
       </c>
       <c r="D40" s="2">
+        <v>13</v>
+      </c>
+      <c r="E40" s="2">
+        <v>12</v>
+      </c>
+      <c r="F40" s="2">
         <v>11</v>
-      </c>
-      <c r="E40" s="2">
-        <v>10</v>
-      </c>
-      <c r="F40" s="2">
-        <v>8</v>
       </c>
       <c r="G40" s="2" t="s">
         <v>13</v>
@@ -1412,16 +1445,16 @@
         <v>10380</v>
       </c>
       <c r="C41" s="2">
-        <v>9.4495000000000005</v>
+        <v>26.453499999999998</v>
       </c>
       <c r="D41" s="2">
+        <v>13</v>
+      </c>
+      <c r="E41" s="2">
         <v>12</v>
       </c>
-      <c r="E41" s="2">
-        <v>10</v>
-      </c>
       <c r="F41" s="2">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="G41" s="2" t="s">
         <v>13</v>
@@ -1435,16 +1468,16 @@
         <v>10390</v>
       </c>
       <c r="C42" s="2">
-        <v>9.6242000000000001</v>
+        <v>27.084900000000001</v>
       </c>
       <c r="D42" s="2">
+        <v>14</v>
+      </c>
+      <c r="E42" s="2">
+        <v>13</v>
+      </c>
+      <c r="F42" s="2">
         <v>12</v>
-      </c>
-      <c r="E42" s="2">
-        <v>10</v>
-      </c>
-      <c r="F42" s="2">
-        <v>9</v>
       </c>
       <c r="G42" s="2" t="s">
         <v>13</v>
@@ -1458,16 +1491,16 @@
         <v>10400</v>
       </c>
       <c r="C43" s="2">
-        <v>9.7982999999999993</v>
+        <v>27.718900000000001</v>
       </c>
       <c r="D43" s="2">
+        <v>14</v>
+      </c>
+      <c r="E43" s="2">
+        <v>13</v>
+      </c>
+      <c r="F43" s="2">
         <v>12</v>
-      </c>
-      <c r="E43" s="2">
-        <v>10</v>
-      </c>
-      <c r="F43" s="2">
-        <v>9</v>
       </c>
       <c r="G43" s="2" t="s">
         <v>13</v>
@@ -1481,16 +1514,16 @@
         <v>10410</v>
       </c>
       <c r="C44" s="2">
-        <v>9.9724000000000004</v>
+        <v>28.3569</v>
       </c>
       <c r="D44" s="2">
+        <v>14</v>
+      </c>
+      <c r="E44" s="2">
+        <v>13</v>
+      </c>
+      <c r="F44" s="2">
         <v>12</v>
-      </c>
-      <c r="E44" s="2">
-        <v>10</v>
-      </c>
-      <c r="F44" s="2">
-        <v>9</v>
       </c>
       <c r="G44" s="2" t="s">
         <v>13</v>
@@ -1504,16 +1537,16 @@
         <v>10420</v>
       </c>
       <c r="C45" s="2">
-        <v>10.1469</v>
+        <v>28.988099999999999</v>
       </c>
       <c r="D45" s="2">
+        <v>14</v>
+      </c>
+      <c r="E45" s="2">
+        <v>13</v>
+      </c>
+      <c r="F45" s="2">
         <v>12</v>
-      </c>
-      <c r="E45" s="2">
-        <v>11</v>
-      </c>
-      <c r="F45" s="2">
-        <v>9</v>
       </c>
       <c r="G45" s="2" t="s">
         <v>13</v>
@@ -1527,16 +1560,16 @@
         <v>10430</v>
       </c>
       <c r="C46" s="2">
-        <v>10.321099999999999</v>
+        <v>29.621500000000001</v>
       </c>
       <c r="D46" s="2">
+        <v>14</v>
+      </c>
+      <c r="E46" s="2">
+        <v>13</v>
+      </c>
+      <c r="F46" s="2">
         <v>12</v>
-      </c>
-      <c r="E46" s="2">
-        <v>11</v>
-      </c>
-      <c r="F46" s="2">
-        <v>9</v>
       </c>
       <c r="G46" s="2" t="s">
         <v>13</v>
@@ -1550,16 +1583,16 @@
         <v>10440</v>
       </c>
       <c r="C47" s="2">
-        <v>10.495900000000001</v>
+        <v>30.2499</v>
       </c>
       <c r="D47" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E47" s="2">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F47" s="2">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G47" s="2" t="s">
         <v>13</v>
@@ -1573,16 +1606,16 @@
         <v>10450</v>
       </c>
       <c r="C48" s="2">
-        <v>10.669499999999999</v>
+        <v>30.888200000000001</v>
       </c>
       <c r="D48" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E48" s="2">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F48" s="2">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G48" s="2" t="s">
         <v>13</v>
@@ -1596,16 +1629,16 @@
         <v>10460</v>
       </c>
       <c r="C49" s="2">
-        <v>10.844200000000001</v>
+        <v>31.526299999999999</v>
       </c>
       <c r="D49" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E49" s="2">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F49" s="2">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="G49" s="2" t="s">
         <v>13</v>
@@ -1619,16 +1652,16 @@
         <v>10470</v>
       </c>
       <c r="C50" s="2">
-        <v>11.0185</v>
+        <v>32.157400000000003</v>
       </c>
       <c r="D50" s="2">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E50" s="2">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F50" s="2">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="G50" s="2" t="s">
         <v>13</v>
@@ -1642,16 +1675,16 @@
         <v>10480</v>
       </c>
       <c r="C51" s="2">
-        <v>11.1927</v>
+        <v>32.783099999999997</v>
       </c>
       <c r="D51" s="2">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E51" s="2">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F51" s="2">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="G51" s="2" t="s">
         <v>13</v>
@@ -1665,16 +1698,16 @@
         <v>10490</v>
       </c>
       <c r="C52" s="2">
-        <v>11.367599999999999</v>
+        <v>33.424300000000002</v>
       </c>
       <c r="D52" s="2">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E52" s="2">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F52" s="2">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="G52" s="2" t="s">
         <v>13</v>
@@ -1688,16 +1721,16 @@
         <v>10500</v>
       </c>
       <c r="C53" s="2">
-        <v>11.541600000000001</v>
+        <v>34.058999999999997</v>
       </c>
       <c r="D53" s="2">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E53" s="2">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F53" s="2">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="G53" s="2" t="s">
         <v>13</v>
@@ -1711,16 +1744,16 @@
         <v>10510</v>
       </c>
       <c r="C54" s="2">
-        <v>11.7158</v>
+        <v>34.693899999999999</v>
       </c>
       <c r="D54" s="2">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E54" s="2">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F54" s="2">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G54" s="2" t="s">
         <v>13</v>
@@ -1734,16 +1767,16 @@
         <v>10520</v>
       </c>
       <c r="C55" s="2">
-        <v>11.889799999999999</v>
+        <v>35.329900000000002</v>
       </c>
       <c r="D55" s="2">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E55" s="2">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F55" s="2">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G55" s="2" t="s">
         <v>13</v>
@@ -1757,16 +1790,16 @@
         <v>10530</v>
       </c>
       <c r="C56" s="2">
-        <v>12.064500000000001</v>
+        <v>35.955800000000004</v>
       </c>
       <c r="D56" s="2">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E56" s="2">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F56" s="2">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G56" s="2" t="s">
         <v>13</v>
@@ -1780,16 +1813,16 @@
         <v>10540</v>
       </c>
       <c r="C57" s="2">
-        <v>12.238799999999999</v>
+        <v>36.591099999999997</v>
       </c>
       <c r="D57" s="2">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E57" s="2">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F57" s="2">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G57" s="2" t="s">
         <v>13</v>
@@ -1803,16 +1836,16 @@
         <v>10550</v>
       </c>
       <c r="C58" s="2">
-        <v>12.4129</v>
+        <v>37.220300000000002</v>
       </c>
       <c r="D58" s="2">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E58" s="2">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F58" s="2">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G58" s="2" t="s">
         <v>13</v>
@@ -1826,16 +1859,16 @@
         <v>10560</v>
       </c>
       <c r="C59" s="2">
-        <v>12.5871</v>
+        <v>37.863300000000002</v>
       </c>
       <c r="D59" s="2">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E59" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F59" s="2">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="G59" s="2" t="s">
         <v>13</v>
@@ -1849,16 +1882,16 @@
         <v>10570</v>
       </c>
       <c r="C60" s="2">
-        <v>12.760999999999999</v>
+        <v>38.496200000000002</v>
       </c>
       <c r="D60" s="2">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E60" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F60" s="2">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="G60" s="2" t="s">
         <v>13</v>
@@ -1872,16 +1905,16 @@
         <v>10580</v>
       </c>
       <c r="C61" s="2">
-        <v>12.935700000000001</v>
+        <v>39.127200000000002</v>
       </c>
       <c r="D61" s="2">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E61" s="2">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F61" s="2">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="G61" s="2" t="s">
         <v>13</v>
@@ -1895,16 +1928,16 @@
         <v>10590</v>
       </c>
       <c r="C62" s="2">
-        <v>13.110200000000001</v>
+        <v>39.766300000000001</v>
       </c>
       <c r="D62" s="2">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E62" s="2">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F62" s="2">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G62" s="2" t="s">
         <v>13</v>
@@ -1918,16 +1951,16 @@
         <v>10600</v>
       </c>
       <c r="C63" s="2">
-        <v>13.2845</v>
+        <v>40.392699999999998</v>
       </c>
       <c r="D63" s="2">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E63" s="2">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F63" s="2">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G63" s="2" t="s">
         <v>13</v>
@@ -1941,16 +1974,16 @@
         <v>10610</v>
       </c>
       <c r="C64" s="2">
-        <v>13.458399999999999</v>
+        <v>41.026299999999999</v>
       </c>
       <c r="D64" s="2">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E64" s="2">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F64" s="2">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G64" s="2" t="s">
         <v>13</v>
@@ -1964,16 +1997,16 @@
         <v>10620</v>
       </c>
       <c r="C65" s="2">
-        <v>13.6328</v>
+        <v>41.66</v>
       </c>
       <c r="D65" s="2">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E65" s="2">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F65" s="2">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G65" s="2" t="s">
         <v>13</v>
@@ -1987,16 +2020,16 @@
         <v>10630</v>
       </c>
       <c r="C66" s="2">
-        <v>13.807499999999999</v>
+        <v>42.2958</v>
       </c>
       <c r="D66" s="2">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E66" s="2">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F66" s="2">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G66" s="2" t="s">
         <v>13</v>
@@ -2010,16 +2043,16 @@
         <v>10640</v>
       </c>
       <c r="C67" s="2">
-        <v>13.981999999999999</v>
+        <v>42.929400000000001</v>
       </c>
       <c r="D67" s="2">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E67" s="2">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F67" s="2">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G67" s="2" t="s">
         <v>13</v>
@@ -2033,16 +2066,16 @@
         <v>10650</v>
       </c>
       <c r="C68" s="2">
-        <v>14.156700000000001</v>
+        <v>43.559800000000003</v>
       </c>
       <c r="D68" s="2">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E68" s="2">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F68" s="2">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G68" s="2" t="s">
         <v>13</v>
@@ -2056,16 +2089,16 @@
         <v>10660</v>
       </c>
       <c r="C69" s="2">
-        <v>14.3307</v>
+        <v>44.199599999999997</v>
       </c>
       <c r="D69" s="2">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E69" s="2">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F69" s="2">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G69" s="2" t="s">
         <v>13</v>
@@ -2079,16 +2112,16 @@
         <v>10670</v>
       </c>
       <c r="C70" s="2">
-        <v>14.505100000000001</v>
+        <v>44.8384</v>
       </c>
       <c r="D70" s="2">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E70" s="2">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F70" s="2">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G70" s="2" t="s">
         <v>13</v>
@@ -2102,16 +2135,16 @@
         <v>10680</v>
       </c>
       <c r="C71" s="2">
-        <v>14.6793</v>
+        <v>45.465000000000003</v>
       </c>
       <c r="D71" s="2">
         <v>16</v>
       </c>
       <c r="E71" s="2">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F71" s="2">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G71" s="2" t="s">
         <v>13</v>
@@ -2125,16 +2158,16 @@
         <v>10690</v>
       </c>
       <c r="C72" s="2">
-        <v>14.853300000000001</v>
+        <v>46.100200000000001</v>
       </c>
       <c r="D72" s="2">
         <v>16</v>
       </c>
       <c r="E72" s="2">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F72" s="2">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G72" s="2" t="s">
         <v>13</v>
@@ -2148,16 +2181,16 @@
         <v>10700</v>
       </c>
       <c r="C73" s="2">
-        <v>15.027900000000001</v>
+        <v>46.7346</v>
       </c>
       <c r="D73" s="2">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E73" s="2">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F73" s="2">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G73" s="2" t="s">
         <v>13</v>
@@ -2171,16 +2204,16 @@
         <v>10710</v>
       </c>
       <c r="C74" s="2">
-        <v>15.202400000000001</v>
+        <v>47.367199999999997</v>
       </c>
       <c r="D74" s="2">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E74" s="2">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F74" s="2">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G74" s="2" t="s">
         <v>13</v>
@@ -2194,16 +2227,16 @@
         <v>10720</v>
       </c>
       <c r="C75" s="2">
-        <v>15.3766</v>
+        <v>48.000799999999998</v>
       </c>
       <c r="D75" s="2">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E75" s="2">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F75" s="2">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G75" s="2" t="s">
         <v>13</v>
@@ -2217,16 +2250,16 @@
         <v>10730</v>
       </c>
       <c r="C76" s="2">
-        <v>15.5504</v>
+        <v>48.630200000000002</v>
       </c>
       <c r="D76" s="2">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E76" s="2">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F76" s="2">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G76" s="2" t="s">
         <v>13</v>
@@ -2240,16 +2273,16 @@
         <v>10740</v>
       </c>
       <c r="C77" s="2">
-        <v>15.725</v>
+        <v>49.2697</v>
       </c>
       <c r="D77" s="2">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E77" s="2">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F77" s="2">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G77" s="2" t="s">
         <v>13</v>
@@ -2263,16 +2296,16 @@
         <v>10750</v>
       </c>
       <c r="C78" s="2">
-        <v>15.8992</v>
+        <v>49.907600000000002</v>
       </c>
       <c r="D78" s="2">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E78" s="2">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F78" s="2">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G78" s="2" t="s">
         <v>13</v>
@@ -2286,16 +2319,16 @@
         <v>10760</v>
       </c>
       <c r="C79" s="2">
-        <v>16.0731</v>
+        <v>50.537399999999998</v>
       </c>
       <c r="D79" s="2">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E79" s="2">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F79" s="2">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G79" s="2" t="s">
         <v>13</v>
@@ -2309,16 +2342,16 @@
         <v>10770</v>
       </c>
       <c r="C80" s="2">
-        <v>16.247599999999998</v>
+        <v>51.179099999999998</v>
       </c>
       <c r="D80" s="2">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E80" s="2">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F80" s="2">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G80" s="2" t="s">
         <v>13</v>
@@ -2332,16 +2365,16 @@
         <v>10780</v>
       </c>
       <c r="C81" s="2">
-        <v>16.4224</v>
+        <v>51.802300000000002</v>
       </c>
       <c r="D81" s="2">
         <v>17</v>
       </c>
       <c r="E81" s="2">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F81" s="2">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G81" s="2" t="s">
         <v>13</v>
@@ -2355,16 +2388,16 @@
         <v>10790</v>
       </c>
       <c r="C82" s="2">
-        <v>16.597000000000001</v>
+        <v>52.432499999999997</v>
       </c>
       <c r="D82" s="2">
         <v>17</v>
       </c>
       <c r="E82" s="2">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F82" s="2">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G82" s="2" t="s">
         <v>13</v>
@@ -2378,16 +2411,16 @@
         <v>10800</v>
       </c>
       <c r="C83" s="2">
-        <v>16.7715</v>
+        <v>53.086399999999998</v>
       </c>
       <c r="D83" s="2">
         <v>17</v>
       </c>
       <c r="E83" s="2">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F83" s="2">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G83" s="2" t="s">
         <v>13</v>
@@ -2401,16 +2434,16 @@
         <v>10810</v>
       </c>
       <c r="C84" s="2">
-        <v>16.945799999999998</v>
+        <v>53.707099999999997</v>
       </c>
       <c r="D84" s="2">
         <v>17</v>
       </c>
       <c r="E84" s="2">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F84" s="2">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G84" s="2" t="s">
         <v>13</v>
@@ -2424,16 +2457,16 @@
         <v>10820</v>
       </c>
       <c r="C85" s="2">
-        <v>17.119700000000002</v>
+        <v>54.330100000000002</v>
       </c>
       <c r="D85" s="2">
         <v>17</v>
       </c>
       <c r="E85" s="2">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F85" s="2">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G85" s="2" t="s">
         <v>13</v>
@@ -2447,16 +2480,16 @@
         <v>10830</v>
       </c>
       <c r="C86" s="2">
-        <v>17.294</v>
+        <v>54.974699999999999</v>
       </c>
       <c r="D86" s="2">
         <v>17</v>
       </c>
       <c r="E86" s="2">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F86" s="2">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G86" s="2" t="s">
         <v>13</v>
@@ -2470,16 +2503,16 @@
         <v>10840</v>
       </c>
       <c r="C87" s="2">
-        <v>17.468499999999999</v>
+        <v>55.616399999999999</v>
       </c>
       <c r="D87" s="2">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E87" s="2">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F87" s="2">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G87" s="2" t="s">
         <v>13</v>
@@ -2493,16 +2526,16 @@
         <v>10850</v>
       </c>
       <c r="C88" s="2">
-        <v>17.6434</v>
+        <v>56.247500000000002</v>
       </c>
       <c r="D88" s="2">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E88" s="2">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F88" s="2">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G88" s="2" t="s">
         <v>13</v>
@@ -2516,16 +2549,16 @@
         <v>10860</v>
       </c>
       <c r="C89" s="2">
-        <v>17.8172</v>
+        <v>56.879300000000001</v>
       </c>
       <c r="D89" s="2">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E89" s="2">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F89" s="2">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G89" s="2" t="s">
         <v>13</v>
@@ -2539,16 +2572,16 @@
         <v>10870</v>
       </c>
       <c r="C90" s="2">
-        <v>17.991499999999998</v>
+        <v>57.512500000000003</v>
       </c>
       <c r="D90" s="2">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E90" s="2">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F90" s="2">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G90" s="2" t="s">
         <v>13</v>
@@ -2562,16 +2595,16 @@
         <v>10880</v>
       </c>
       <c r="C91" s="2">
-        <v>18.165199999999999</v>
+        <v>58.144399999999997</v>
       </c>
       <c r="D91" s="2">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E91" s="2">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F91" s="2">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G91" s="2" t="s">
         <v>13</v>
@@ -2585,16 +2618,16 @@
         <v>10890</v>
       </c>
       <c r="C92" s="2">
-        <v>18.339400000000001</v>
+        <v>58.780299999999997</v>
       </c>
       <c r="D92" s="2">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E92" s="2">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F92" s="2">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G92" s="2" t="s">
         <v>13</v>
@@ -2608,16 +2641,16 @@
         <v>10900</v>
       </c>
       <c r="C93" s="2">
-        <v>18.513400000000001</v>
+        <v>59.411900000000003</v>
       </c>
       <c r="D93" s="2">
         <v>18</v>
       </c>
       <c r="E93" s="2">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F93" s="2">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G93" s="2" t="s">
         <v>13</v>
@@ -2631,16 +2664,16 @@
         <v>10910</v>
       </c>
       <c r="C94" s="2">
-        <v>18.688700000000001</v>
+        <v>60.042499999999997</v>
       </c>
       <c r="D94" s="2">
         <v>18</v>
       </c>
       <c r="E94" s="2">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F94" s="2">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G94" s="2" t="s">
         <v>13</v>
@@ -2654,16 +2687,16 @@
         <v>10920</v>
       </c>
       <c r="C95" s="2">
-        <v>18.863099999999999</v>
+        <v>60.6768</v>
       </c>
       <c r="D95" s="2">
         <v>18</v>
       </c>
       <c r="E95" s="2">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F95" s="2">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G95" s="2" t="s">
         <v>13</v>
@@ -2677,16 +2710,16 @@
         <v>10930</v>
       </c>
       <c r="C96" s="2">
-        <v>19.036899999999999</v>
+        <v>61.315399999999997</v>
       </c>
       <c r="D96" s="2">
         <v>18</v>
       </c>
       <c r="E96" s="2">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F96" s="2">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G96" s="2" t="s">
         <v>13</v>
@@ -2700,16 +2733,16 @@
         <v>10940</v>
       </c>
       <c r="C97" s="2">
-        <v>19.210699999999999</v>
+        <v>61.947099999999999</v>
       </c>
       <c r="D97" s="2">
         <v>18</v>
       </c>
       <c r="E97" s="2">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F97" s="2">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G97" s="2" t="s">
         <v>13</v>
@@ -2723,16 +2756,16 @@
         <v>10950</v>
       </c>
       <c r="C98" s="2">
-        <v>19.385200000000001</v>
+        <v>62.582799999999999</v>
       </c>
       <c r="D98" s="2">
         <v>18</v>
       </c>
       <c r="E98" s="2">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F98" s="2">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G98" s="2" t="s">
         <v>13</v>
@@ -2746,16 +2779,16 @@
         <v>10960</v>
       </c>
       <c r="C99" s="2">
-        <v>19.559899999999999</v>
+        <v>63.206499999999998</v>
       </c>
       <c r="D99" s="2">
         <v>18</v>
       </c>
       <c r="E99" s="2">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F99" s="2">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G99" s="2" t="s">
         <v>13</v>
@@ -2769,7 +2802,7 @@
         <v>10970</v>
       </c>
       <c r="C100" s="2">
-        <v>19.733699999999999</v>
+        <v>63.8491</v>
       </c>
       <c r="D100" s="2">
         <v>18</v>
@@ -2778,7 +2811,7 @@
         <v>17</v>
       </c>
       <c r="F100" s="2">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G100" s="2" t="s">
         <v>13</v>
@@ -2792,7 +2825,7 @@
         <v>10980</v>
       </c>
       <c r="C101" s="2">
-        <v>19.907800000000002</v>
+        <v>64.475200000000001</v>
       </c>
       <c r="D101" s="2">
         <v>18</v>
@@ -2801,7 +2834,7 @@
         <v>17</v>
       </c>
       <c r="F101" s="2">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G101" s="2" t="s">
         <v>13</v>
@@ -2815,7 +2848,7 @@
         <v>10990</v>
       </c>
       <c r="C102" s="2">
-        <v>20.0822</v>
+        <v>65.112899999999996</v>
       </c>
       <c r="D102" s="2">
         <v>18</v>
@@ -2824,7 +2857,7 @@
         <v>17</v>
       </c>
       <c r="F102" s="2">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="G102" s="2" t="s">
         <v>13</v>
@@ -2838,7 +2871,7 @@
         <v>11000</v>
       </c>
       <c r="C103" s="2">
-        <v>20.198699999999999</v>
+        <v>65.531400000000005</v>
       </c>
       <c r="D103" s="2">
         <v>18</v>
@@ -2847,7 +2880,7 @@
         <v>17</v>
       </c>
       <c r="F103" s="2">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="G103" s="2" t="s">
         <v>13</v>

--- a/LubanConfig/MiniTemplate/Datas/生成数据/#关卡设计表_1导.xlsx
+++ b/LubanConfig/MiniTemplate/Datas/生成数据/#关卡设计表_1导.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="212" uniqueCount="24">
   <si>
     <t>##var</t>
   </si>
@@ -106,15 +106,7 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Lava</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Skyland</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Winter</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -717,7 +709,7 @@
         <v>18</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.15">
@@ -736,12 +728,8 @@
       <c r="F9" s="2">
         <v>4</v>
       </c>
-      <c r="G9" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="H9" s="3" t="s">
-        <v>25</v>
-      </c>
+      <c r="G9" s="2"/>
+      <c r="H9" s="3"/>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.15">
       <c r="B10" s="2">
@@ -759,12 +747,8 @@
       <c r="F10" s="2">
         <v>4</v>
       </c>
-      <c r="G10" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>23</v>
-      </c>
+      <c r="G10" s="2"/>
+      <c r="H10" s="3"/>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.15">
       <c r="B11" s="2">

--- a/LubanConfig/MiniTemplate/Datas/生成数据/#关卡设计表_1导.xlsx
+++ b/LubanConfig/MiniTemplate/Datas/生成数据/#关卡设计表_1导.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="212" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="27">
   <si>
     <t>##var</t>
   </si>
@@ -60,53 +60,47 @@
     <t>##</t>
   </si>
   <si>
-    <t/>
+    <t>普通</t>
+  </si>
+  <si>
+    <t>Lava</t>
+  </si>
+  <si>
+    <t>极难</t>
+  </si>
+  <si>
+    <t>Autumn</t>
   </si>
   <si>
     <t>简单</t>
   </si>
   <si>
-    <t>普通</t>
+    <t>Skyland</t>
+  </si>
+  <si>
+    <t>Winter</t>
+  </si>
+  <si>
+    <t>很难</t>
+  </si>
+  <si>
+    <t>Darkland</t>
+  </si>
+  <si>
+    <t>Desert</t>
+  </si>
+  <si>
+    <t>Forest</t>
   </si>
   <si>
     <t>困难</t>
   </si>
   <si>
-    <t>很难</t>
-  </si>
-  <si>
-    <t>极难</t>
-  </si>
-  <si>
-    <t>Forest</t>
+    <t>简单</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Autumn</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Desert</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>D</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>arkland</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Skyland</t>
+    <t>普通</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -134,14 +128,12 @@
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
@@ -613,11 +605,11 @@
       <c r="F4" s="2">
         <v>1</v>
       </c>
-      <c r="G4" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="H4" s="3" t="s">
-        <v>19</v>
+      <c r="G4" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.15">
@@ -636,11 +628,11 @@
       <c r="F5" s="2">
         <v>1</v>
       </c>
-      <c r="G5" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="H5" s="3" t="s">
-        <v>20</v>
+      <c r="G5" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.15">
@@ -659,11 +651,11 @@
       <c r="F6" s="2">
         <v>2</v>
       </c>
-      <c r="G6" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="H6" s="3" t="s">
-        <v>21</v>
+      <c r="G6" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.15">
@@ -682,11 +674,11 @@
       <c r="F7" s="2">
         <v>2</v>
       </c>
-      <c r="G7" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="H7" s="3" t="s">
-        <v>22</v>
+      <c r="G7" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.15">
@@ -705,11 +697,11 @@
       <c r="F8" s="2">
         <v>3</v>
       </c>
-      <c r="G8" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="H8" s="3" t="s">
-        <v>23</v>
+      <c r="G8" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.15">
@@ -728,8 +720,12 @@
       <c r="F9" s="2">
         <v>4</v>
       </c>
-      <c r="G9" s="2"/>
-      <c r="H9" s="3"/>
+      <c r="G9" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>21</v>
+      </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.15">
       <c r="B10" s="2">
@@ -747,8 +743,12 @@
       <c r="F10" s="2">
         <v>4</v>
       </c>
-      <c r="G10" s="2"/>
-      <c r="H10" s="3"/>
+      <c r="G10" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.15">
       <c r="B11" s="2">
@@ -766,8 +766,12 @@
       <c r="F11" s="2">
         <v>5</v>
       </c>
-      <c r="G11" s="2"/>
-      <c r="H11" s="2"/>
+      <c r="G11" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.15">
       <c r="B12" s="2">
@@ -785,8 +789,12 @@
       <c r="F12" s="2">
         <v>5</v>
       </c>
-      <c r="G12" s="2"/>
-      <c r="H12" s="2"/>
+      <c r="G12" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>19</v>
+      </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.15">
       <c r="B13" s="2">
@@ -804,8 +812,12 @@
       <c r="F13" s="2">
         <v>5</v>
       </c>
-      <c r="G13" s="2"/>
-      <c r="H13" s="2"/>
+      <c r="G13" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.15">
       <c r="B14" s="2">
@@ -823,8 +835,12 @@
       <c r="F14" s="2">
         <v>6</v>
       </c>
-      <c r="G14" s="2"/>
-      <c r="H14" s="2"/>
+      <c r="G14" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>23</v>
+      </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.15">
       <c r="B15" s="2">
@@ -846,7 +862,7 @@
         <v>13</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.15">
@@ -866,10 +882,10 @@
         <v>7</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="17" spans="2:8" x14ac:dyDescent="0.15">
@@ -892,7 +908,7 @@
         <v>13</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
     </row>
     <row r="18" spans="2:8" x14ac:dyDescent="0.15">
@@ -915,7 +931,7 @@
         <v>13</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="19" spans="2:8" x14ac:dyDescent="0.15">
@@ -935,10 +951,10 @@
         <v>7</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
     </row>
     <row r="20" spans="2:8" x14ac:dyDescent="0.15">
@@ -958,10 +974,10 @@
         <v>8</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
     </row>
     <row r="21" spans="2:8" x14ac:dyDescent="0.15">
@@ -984,7 +1000,7 @@
         <v>13</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
     </row>
     <row r="22" spans="2:8" x14ac:dyDescent="0.15">
@@ -1004,10 +1020,10 @@
         <v>8</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
     </row>
     <row r="23" spans="2:8" x14ac:dyDescent="0.15">
@@ -1030,7 +1046,7 @@
         <v>13</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
     </row>
     <row r="24" spans="2:8" x14ac:dyDescent="0.15">
@@ -1050,10 +1066,10 @@
         <v>9</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="25" spans="2:8" x14ac:dyDescent="0.15">
@@ -1073,10 +1089,10 @@
         <v>9</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
     </row>
     <row r="26" spans="2:8" x14ac:dyDescent="0.15">
@@ -1096,10 +1112,10 @@
         <v>9</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
     </row>
     <row r="27" spans="2:8" x14ac:dyDescent="0.15">
@@ -1119,10 +1135,10 @@
         <v>9</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="28" spans="2:8" x14ac:dyDescent="0.15">
@@ -1145,7 +1161,7 @@
         <v>13</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
     </row>
     <row r="29" spans="2:8" x14ac:dyDescent="0.15">
@@ -1165,10 +1181,10 @@
         <v>10</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="30" spans="2:8" x14ac:dyDescent="0.15">
@@ -1188,10 +1204,10 @@
         <v>10</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
     </row>
     <row r="31" spans="2:8" x14ac:dyDescent="0.15">
@@ -1214,7 +1230,7 @@
         <v>13</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
     </row>
     <row r="32" spans="2:8" x14ac:dyDescent="0.15">
@@ -1234,10 +1250,10 @@
         <v>10</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="H32" s="2" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
     </row>
     <row r="33" spans="2:8" x14ac:dyDescent="0.15">
@@ -1260,7 +1276,7 @@
         <v>13</v>
       </c>
       <c r="H33" s="2" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
     </row>
     <row r="34" spans="2:8" x14ac:dyDescent="0.15">
@@ -1280,10 +1296,10 @@
         <v>11</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="H34" s="2" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="35" spans="2:8" x14ac:dyDescent="0.15">
@@ -1303,10 +1319,10 @@
         <v>11</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="H35" s="2" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
     </row>
     <row r="36" spans="2:8" x14ac:dyDescent="0.15">
@@ -1326,10 +1342,10 @@
         <v>11</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="H36" s="2" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
     </row>
     <row r="37" spans="2:8" x14ac:dyDescent="0.15">
@@ -1349,10 +1365,10 @@
         <v>11</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="H37" s="2" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
     </row>
     <row r="38" spans="2:8" x14ac:dyDescent="0.15">
@@ -1372,10 +1388,10 @@
         <v>11</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="H38" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="39" spans="2:8" x14ac:dyDescent="0.15">
@@ -1395,10 +1411,10 @@
         <v>11</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="H39" s="2" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
     </row>
     <row r="40" spans="2:8" x14ac:dyDescent="0.15">
@@ -1421,7 +1437,7 @@
         <v>13</v>
       </c>
       <c r="H40" s="2" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
     </row>
     <row r="41" spans="2:8" x14ac:dyDescent="0.15">
@@ -1441,10 +1457,10 @@
         <v>12</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="H41" s="2" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
     </row>
     <row r="42" spans="2:8" x14ac:dyDescent="0.15">
@@ -1467,7 +1483,7 @@
         <v>13</v>
       </c>
       <c r="H42" s="2" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="43" spans="2:8" x14ac:dyDescent="0.15">
@@ -1487,10 +1503,10 @@
         <v>12</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="H43" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="44" spans="2:8" x14ac:dyDescent="0.15">
@@ -1510,10 +1526,10 @@
         <v>12</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="H44" s="2" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
     </row>
     <row r="45" spans="2:8" x14ac:dyDescent="0.15">
@@ -1533,10 +1549,10 @@
         <v>12</v>
       </c>
       <c r="G45" s="2" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="H45" s="2" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
     </row>
     <row r="46" spans="2:8" x14ac:dyDescent="0.15">
@@ -1559,7 +1575,7 @@
         <v>13</v>
       </c>
       <c r="H46" s="2" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
     </row>
     <row r="47" spans="2:8" x14ac:dyDescent="0.15">
@@ -1579,10 +1595,10 @@
         <v>12</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="H47" s="2" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
     </row>
     <row r="48" spans="2:8" x14ac:dyDescent="0.15">
@@ -1605,7 +1621,7 @@
         <v>13</v>
       </c>
       <c r="H48" s="2" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="49" spans="2:8" x14ac:dyDescent="0.15">
@@ -1625,10 +1641,10 @@
         <v>13</v>
       </c>
       <c r="G49" s="2" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="H49" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="50" spans="2:8" x14ac:dyDescent="0.15">
@@ -1648,10 +1664,10 @@
         <v>13</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="H50" s="2" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
     </row>
     <row r="51" spans="2:8" x14ac:dyDescent="0.15">
@@ -1671,10 +1687,10 @@
         <v>13</v>
       </c>
       <c r="G51" s="2" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="H51" s="2" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
     </row>
     <row r="52" spans="2:8" x14ac:dyDescent="0.15">
@@ -1694,10 +1710,10 @@
         <v>13</v>
       </c>
       <c r="G52" s="2" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="H52" s="2" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
     </row>
     <row r="53" spans="2:8" x14ac:dyDescent="0.15">
@@ -1720,7 +1736,7 @@
         <v>13</v>
       </c>
       <c r="H53" s="2" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="54" spans="2:8" x14ac:dyDescent="0.15">
@@ -1740,10 +1756,10 @@
         <v>13</v>
       </c>
       <c r="G54" s="2" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="H54" s="2" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
     </row>
     <row r="55" spans="2:8" x14ac:dyDescent="0.15">
@@ -1763,10 +1779,10 @@
         <v>13</v>
       </c>
       <c r="G55" s="2" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="H55" s="2" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
     </row>
     <row r="56" spans="2:8" x14ac:dyDescent="0.15">
@@ -1786,10 +1802,10 @@
         <v>13</v>
       </c>
       <c r="G56" s="2" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="H56" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="57" spans="2:8" x14ac:dyDescent="0.15">
@@ -1812,7 +1828,7 @@
         <v>13</v>
       </c>
       <c r="H57" s="2" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
     </row>
     <row r="58" spans="2:8" x14ac:dyDescent="0.15">
@@ -1832,10 +1848,10 @@
         <v>13</v>
       </c>
       <c r="G58" s="2" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="H58" s="2" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
     </row>
     <row r="59" spans="2:8" x14ac:dyDescent="0.15">
@@ -1858,7 +1874,7 @@
         <v>13</v>
       </c>
       <c r="H59" s="2" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
     </row>
     <row r="60" spans="2:8" x14ac:dyDescent="0.15">
@@ -1878,10 +1894,10 @@
         <v>14</v>
       </c>
       <c r="G60" s="2" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="H60" s="2" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
     </row>
     <row r="61" spans="2:8" x14ac:dyDescent="0.15">
@@ -1904,7 +1920,7 @@
         <v>13</v>
       </c>
       <c r="H61" s="2" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="62" spans="2:8" x14ac:dyDescent="0.15">
@@ -1924,10 +1940,10 @@
         <v>14</v>
       </c>
       <c r="G62" s="2" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="H62" s="2" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
     </row>
     <row r="63" spans="2:8" x14ac:dyDescent="0.15">
@@ -1950,7 +1966,7 @@
         <v>13</v>
       </c>
       <c r="H63" s="2" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
     </row>
     <row r="64" spans="2:8" x14ac:dyDescent="0.15">
@@ -1970,10 +1986,10 @@
         <v>14</v>
       </c>
       <c r="G64" s="2" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="H64" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="65" spans="2:8" x14ac:dyDescent="0.15">
@@ -1996,7 +2012,7 @@
         <v>13</v>
       </c>
       <c r="H65" s="2" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
     </row>
     <row r="66" spans="2:8" x14ac:dyDescent="0.15">
@@ -2016,10 +2032,10 @@
         <v>14</v>
       </c>
       <c r="G66" s="2" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="H66" s="2" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
     </row>
     <row r="67" spans="2:8" x14ac:dyDescent="0.15">
@@ -2042,7 +2058,7 @@
         <v>13</v>
       </c>
       <c r="H67" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="68" spans="2:8" x14ac:dyDescent="0.15">
@@ -2062,10 +2078,10 @@
         <v>14</v>
       </c>
       <c r="G68" s="2" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="H68" s="2" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
     </row>
     <row r="69" spans="2:8" x14ac:dyDescent="0.15">
@@ -2085,10 +2101,10 @@
         <v>14</v>
       </c>
       <c r="G69" s="2" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="H69" s="2" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
     </row>
     <row r="70" spans="2:8" x14ac:dyDescent="0.15">
@@ -2108,10 +2124,10 @@
         <v>14</v>
       </c>
       <c r="G70" s="2" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="H70" s="2" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
     </row>
     <row r="71" spans="2:8" x14ac:dyDescent="0.15">
@@ -2131,10 +2147,10 @@
         <v>15</v>
       </c>
       <c r="G71" s="2" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="H71" s="2" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="72" spans="2:8" x14ac:dyDescent="0.15">
@@ -2154,10 +2170,10 @@
         <v>15</v>
       </c>
       <c r="G72" s="2" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="H72" s="2" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
     </row>
     <row r="73" spans="2:8" x14ac:dyDescent="0.15">
@@ -2177,10 +2193,10 @@
         <v>15</v>
       </c>
       <c r="G73" s="2" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="H73" s="2" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
     </row>
     <row r="74" spans="2:8" x14ac:dyDescent="0.15">
@@ -2203,7 +2219,7 @@
         <v>13</v>
       </c>
       <c r="H74" s="2" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
     </row>
     <row r="75" spans="2:8" x14ac:dyDescent="0.15">
@@ -2223,10 +2239,10 @@
         <v>15</v>
       </c>
       <c r="G75" s="2" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="H75" s="2" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
     </row>
     <row r="76" spans="2:8" x14ac:dyDescent="0.15">
@@ -2246,10 +2262,10 @@
         <v>15</v>
       </c>
       <c r="G76" s="2" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="H76" s="2" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
     </row>
     <row r="77" spans="2:8" x14ac:dyDescent="0.15">
@@ -2269,10 +2285,10 @@
         <v>15</v>
       </c>
       <c r="G77" s="2" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="H77" s="2" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
     </row>
     <row r="78" spans="2:8" x14ac:dyDescent="0.15">
@@ -2292,10 +2308,10 @@
         <v>15</v>
       </c>
       <c r="G78" s="2" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="H78" s="2" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="79" spans="2:8" x14ac:dyDescent="0.15">
@@ -2315,10 +2331,10 @@
         <v>15</v>
       </c>
       <c r="G79" s="2" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="H79" s="2" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
     </row>
     <row r="80" spans="2:8" x14ac:dyDescent="0.15">
@@ -2338,10 +2354,10 @@
         <v>15</v>
       </c>
       <c r="G80" s="2" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="H80" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="81" spans="2:8" x14ac:dyDescent="0.15">
@@ -2361,10 +2377,10 @@
         <v>15</v>
       </c>
       <c r="G81" s="2" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="H81" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="82" spans="2:8" x14ac:dyDescent="0.15">
@@ -2387,7 +2403,7 @@
         <v>13</v>
       </c>
       <c r="H82" s="2" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
     </row>
     <row r="83" spans="2:8" x14ac:dyDescent="0.15">
@@ -2407,10 +2423,10 @@
         <v>15</v>
       </c>
       <c r="G83" s="2" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="H83" s="2" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
     </row>
     <row r="84" spans="2:8" x14ac:dyDescent="0.15">
@@ -2433,7 +2449,7 @@
         <v>13</v>
       </c>
       <c r="H84" s="2" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
     </row>
     <row r="85" spans="2:8" x14ac:dyDescent="0.15">
@@ -2453,10 +2469,10 @@
         <v>16</v>
       </c>
       <c r="G85" s="2" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="H85" s="2" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
     </row>
     <row r="86" spans="2:8" x14ac:dyDescent="0.15">
@@ -2476,10 +2492,10 @@
         <v>16</v>
       </c>
       <c r="G86" s="2" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="H86" s="2" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="87" spans="2:8" x14ac:dyDescent="0.15">
@@ -2499,10 +2515,10 @@
         <v>16</v>
       </c>
       <c r="G87" s="2" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="H87" s="2" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
     </row>
     <row r="88" spans="2:8" x14ac:dyDescent="0.15">
@@ -2522,10 +2538,10 @@
         <v>16</v>
       </c>
       <c r="G88" s="2" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="H88" s="2" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
     </row>
     <row r="89" spans="2:8" x14ac:dyDescent="0.15">
@@ -2545,10 +2561,10 @@
         <v>16</v>
       </c>
       <c r="G89" s="2" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="H89" s="2" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
     </row>
     <row r="90" spans="2:8" x14ac:dyDescent="0.15">
@@ -2571,7 +2587,7 @@
         <v>13</v>
       </c>
       <c r="H90" s="2" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="91" spans="2:8" x14ac:dyDescent="0.15">
@@ -2591,10 +2607,10 @@
         <v>16</v>
       </c>
       <c r="G91" s="2" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="H91" s="2" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
     </row>
     <row r="92" spans="2:8" x14ac:dyDescent="0.15">
@@ -2614,10 +2630,10 @@
         <v>16</v>
       </c>
       <c r="G92" s="2" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="H92" s="2" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
     </row>
     <row r="93" spans="2:8" x14ac:dyDescent="0.15">
@@ -2637,10 +2653,10 @@
         <v>16</v>
       </c>
       <c r="G93" s="2" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="H93" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="94" spans="2:8" x14ac:dyDescent="0.15">
@@ -2660,10 +2676,10 @@
         <v>16</v>
       </c>
       <c r="G94" s="2" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="H94" s="2" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
     </row>
     <row r="95" spans="2:8" x14ac:dyDescent="0.15">
@@ -2683,10 +2699,10 @@
         <v>16</v>
       </c>
       <c r="G95" s="2" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="H95" s="2" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
     </row>
     <row r="96" spans="2:8" x14ac:dyDescent="0.15">
@@ -2706,10 +2722,10 @@
         <v>16</v>
       </c>
       <c r="G96" s="2" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="H96" s="2" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
     </row>
     <row r="97" spans="2:8" x14ac:dyDescent="0.15">
@@ -2729,10 +2745,10 @@
         <v>16</v>
       </c>
       <c r="G97" s="2" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="H97" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="98" spans="2:8" x14ac:dyDescent="0.15">
@@ -2752,10 +2768,10 @@
         <v>16</v>
       </c>
       <c r="G98" s="2" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="H98" s="2" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
     </row>
     <row r="99" spans="2:8" x14ac:dyDescent="0.15">
@@ -2775,10 +2791,10 @@
         <v>16</v>
       </c>
       <c r="G99" s="2" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="H99" s="2" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="100" spans="2:8" x14ac:dyDescent="0.15">
@@ -2798,10 +2814,10 @@
         <v>16</v>
       </c>
       <c r="G100" s="2" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="H100" s="2" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
     </row>
     <row r="101" spans="2:8" x14ac:dyDescent="0.15">
@@ -2821,10 +2837,10 @@
         <v>16</v>
       </c>
       <c r="G101" s="2" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="H101" s="2" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
     </row>
     <row r="102" spans="2:8" x14ac:dyDescent="0.15">
@@ -2844,10 +2860,10 @@
         <v>17</v>
       </c>
       <c r="G102" s="2" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="H102" s="2" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
     </row>
     <row r="103" spans="2:8" x14ac:dyDescent="0.15">
@@ -2855,7 +2871,7 @@
         <v>11000</v>
       </c>
       <c r="C103" s="2">
-        <v>65.531400000000005</v>
+        <v>65.131399999999999</v>
       </c>
       <c r="D103" s="2">
         <v>18</v>
@@ -2867,10 +2883,10 @@
         <v>17</v>
       </c>
       <c r="G103" s="2" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="H103" s="2" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
     </row>
   </sheetData>
